--- a/weekly_temp/patents_量子科技长三角产业创新中心.xlsx
+++ b/weekly_temp/patents_量子科技长三角产业创新中心.xlsx
@@ -413,84 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>applicant</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>inventor</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>abstract</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>url</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>一种场路协同仿真方法、系统、介质及电子设备</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>量子科技长三角产业创新中心</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>王西伟 | 丁大志 | 张天成 | 包华广 | 张岩 | 许雅烽</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>公开专利</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>本发明公开了一种场路协同仿真方法、系统、介质及电子设备，包括：获取参数数据，基于参数数据，建立约瑟夫森结等效电路，约瑟夫森结等效电路基于约瑟夫森结在超导状态下的磁通量子化和隧穿效应建立；约瑟夫森结等效电路通过电磁仿真算法更新电磁场，进行场路协同处理，得到作用于电磁场下的传输线模型；基于传输线模型建立传输线仿真电路，对传输线仿真电路进行脉冲调制获取电流数据，基于电流数据处理得到场路协同下的约瑟夫森结电流曲线；通过对约瑟夫森结等效电路进行场路协同处理，获取约瑟夫森结电流曲线，实现了对超导量子芯片中约瑟夫森结等效电感的精确仿真，不仅提高了仿真精度，还能够显著提升超导量子芯片优化水平。</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=5f0032b3-5aaa-4182-a255-edcf9007d1a6&amp;shareId=9152F090-E032-685C-B5E4-F8DB324DD0F7&amp;from=EXPORT&amp;signature=yf6JIDxe9xOJ2Ksu%2FMkqb7O%2B83c6%2FPDGdHy841SFgvw%3D&amp;expire=94608000&amp;date=20260529T004829Z&amp;version=1.0</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/weekly_temp/patents_量子科技长三角产业创新中心.xlsx
+++ b/weekly_temp/patents_量子科技长三角产业创新中心.xlsx
@@ -413,9 +413,158 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>applicant</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>inventor</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>abstract</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>一种超导量子比特量子态读取方法、装置、设备及介质</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>量子科技长三角产业创新中心</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>周慧德 | 李泽东 | 王天骐 | 栾添 | 潘文杰</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>授权专利</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>本发明涉及量子比特读取领域，特别是涉及一种超导量子比特量子态读取方法、装置、设备及介质，通过向超导量子芯片发送读取驱动信号；所述读取驱动信号为包括超导量子比特的|0&amp;gt;态谐振频率及|1&amp;gt;态谐振频率的变频信号；从所述超导量子芯片采集读取反馈信号；根据所述读取反馈信号、预存储的对应所述读取驱动信号的|0&amp;gt;态响应信号及|1&amp;gt;态响应信号，通过相关性分析确定所述超导量子比特的量子态。本发明使用变频信号作为所述读取驱动信号，能减低系统对于频率无关噪声的敏感，提升信号的信噪比，还有，相关性计算不需要再转换到IQ平面，减少了计算的步骤，且相关分析的算法通常可以使用硬件加速，降低了解算的资源消耗，提升了运算效率。</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=06b69bba-8a14-46cc-b46d-69ba25bcb8cb&amp;shareId=4112G6DD-E305-7121-1F1F-46748E576683&amp;from=EXPORT&amp;signature=jKfqmW%2BQ91OksO438Zzu8O6JpaCtxIjj9lq%2FUQ8cS%2Bc%3D&amp;expire=94608000&amp;date=20260717T011141Z&amp;version=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>量子比特映射方法、装置和计算机设备</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>量子科技长三角产业创新中心</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>许诺佳 | 何雨宸 | 张泽阳 | 黄泓凯 | 张会凯</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>公开专利</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>本申请涉及一种量子比特映射方法，包括：获取量子芯片中多个量子比特之间的耦合关系；对量子芯片的量子线路进行划分，得到依次排列的多个子线路；确定量子线路对应的第一子线路集和第二子线路集；第二子线路集的第二子线路组，包含第一子线路集的至少两个相邻的第一子线路组，第一子线路组包括至少一个子线路；对各第二子线路组所属的线路段，基于耦合关系，确定线路段的第一量子比特映射结果和第二量子比特映射结果；从第一量子比特映射结果和第二量子比特映射结果中，确定比特门添加数量较少的第一目标量子比特映射结果；按照各线路段在量子线路中的排列顺序，依次拼接各线路段的第一目标量子比特映射结果，得到量子线路的量子比特映射结果。</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=62bc2a4e-b249-4c70-a07e-9914a0c3ce44&amp;shareId=4112G6DD-E305-7121-1F1F-46748E576683&amp;from=EXPORT&amp;signature=wjxOyzm7an%2BfBI2mFDbRHmGns2lKl6Z6rUQ5dB5Y6Pk%3D&amp;expire=94608000&amp;date=20260717T011141Z&amp;version=1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>一种用于量子芯片的参数校准方法及系统</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>量子科技长三角产业创新中心 | 中电科国基量子产业(苏州)有限公司</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>陈玉光 | 王碧莹</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>公开专利</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>本公开提供了一种用于量子芯片的参数校准方法及系统，方法包括获取校准的原始数据；对原始数据进行第一层级评估，若数据质量不满足标准则执行第一重试策略，调整硬件参数重新获取数据；若满足标准则对中间分析结果进行第二层级评估，若结果不满足标准则判定失效类型；若为实验参数失配则执行第一重试策略，若为算法失配则执行第二重试策略调整算法；当双重评估均通过时输出最终校准参数，校准方法将输出参数应用于量子芯片。本公开通过双重评估与两级重试，提升校准成功率与准确性。</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=5b6aca0e-9969-4dc7-b092-f307debaa46f&amp;shareId=4112G6DD-E305-7121-1F1F-46748E576683&amp;from=EXPORT&amp;signature=9LkTlkPVAZB%2Bd6eJcT0obAPgbJzI2kLSL3TMT8zowRk%3D&amp;expire=94608000&amp;date=20260717T011141Z&amp;version=1.0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/weekly_temp/patents_量子科技长三角产业创新中心.xlsx
+++ b/weekly_temp/patents_量子科技长三角产业创新中心.xlsx
@@ -413,158 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>applicant</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>inventor</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>abstract</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>url</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>一种超导量子比特量子态读取方法、装置、设备及介质</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>量子科技长三角产业创新中心</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>周慧德 | 李泽东 | 王天骐 | 栾添 | 潘文杰</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>授权专利</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>本发明涉及量子比特读取领域，特别是涉及一种超导量子比特量子态读取方法、装置、设备及介质，通过向超导量子芯片发送读取驱动信号；所述读取驱动信号为包括超导量子比特的|0&amp;gt;态谐振频率及|1&amp;gt;态谐振频率的变频信号；从所述超导量子芯片采集读取反馈信号；根据所述读取反馈信号、预存储的对应所述读取驱动信号的|0&amp;gt;态响应信号及|1&amp;gt;态响应信号，通过相关性分析确定所述超导量子比特的量子态。本发明使用变频信号作为所述读取驱动信号，能减低系统对于频率无关噪声的敏感，提升信号的信噪比，还有，相关性计算不需要再转换到IQ平面，减少了计算的步骤，且相关分析的算法通常可以使用硬件加速，降低了解算的资源消耗，提升了运算效率。</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=06b69bba-8a14-46cc-b46d-69ba25bcb8cb&amp;shareId=4112G6DD-E305-7121-1F1F-46748E576683&amp;from=EXPORT&amp;signature=jKfqmW%2BQ91OksO438Zzu8O6JpaCtxIjj9lq%2FUQ8cS%2Bc%3D&amp;expire=94608000&amp;date=20260717T011141Z&amp;version=1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>量子比特映射方法、装置和计算机设备</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>量子科技长三角产业创新中心</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>许诺佳 | 何雨宸 | 张泽阳 | 黄泓凯 | 张会凯</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>公开专利</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>本申请涉及一种量子比特映射方法，包括：获取量子芯片中多个量子比特之间的耦合关系；对量子芯片的量子线路进行划分，得到依次排列的多个子线路；确定量子线路对应的第一子线路集和第二子线路集；第二子线路集的第二子线路组，包含第一子线路集的至少两个相邻的第一子线路组，第一子线路组包括至少一个子线路；对各第二子线路组所属的线路段，基于耦合关系，确定线路段的第一量子比特映射结果和第二量子比特映射结果；从第一量子比特映射结果和第二量子比特映射结果中，确定比特门添加数量较少的第一目标量子比特映射结果；按照各线路段在量子线路中的排列顺序，依次拼接各线路段的第一目标量子比特映射结果，得到量子线路的量子比特映射结果。</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=62bc2a4e-b249-4c70-a07e-9914a0c3ce44&amp;shareId=4112G6DD-E305-7121-1F1F-46748E576683&amp;from=EXPORT&amp;signature=wjxOyzm7an%2BfBI2mFDbRHmGns2lKl6Z6rUQ5dB5Y6Pk%3D&amp;expire=94608000&amp;date=20260717T011141Z&amp;version=1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>一种用于量子芯片的参数校准方法及系统</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>量子科技长三角产业创新中心 | 中电科国基量子产业(苏州)有限公司</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>陈玉光 | 王碧莹</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>公开专利</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>本公开提供了一种用于量子芯片的参数校准方法及系统，方法包括获取校准的原始数据；对原始数据进行第一层级评估，若数据质量不满足标准则执行第一重试策略，调整硬件参数重新获取数据；若满足标准则对中间分析结果进行第二层级评估，若结果不满足标准则判定失效类型；若为实验参数失配则执行第一重试策略，若为算法失配则执行第二重试策略调整算法；当双重评估均通过时输出最终校准参数，校准方法将输出参数应用于量子芯片。本公开通过双重评估与两级重试，提升校准成功率与准确性。</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://analytics.zhihuiya.com/patent-view/abst?patentId=5b6aca0e-9969-4dc7-b092-f307debaa46f&amp;shareId=4112G6DD-E305-7121-1F1F-46748E576683&amp;from=EXPORT&amp;signature=9LkTlkPVAZB%2Bd6eJcT0obAPgbJzI2kLSL3TMT8zowRk%3D&amp;expire=94608000&amp;date=20260717T011141Z&amp;version=1.0</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>